--- a/Result/checksun_type/中央處理器.xlsx
+++ b/Result/checksun_type/中央處理器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>45.73</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>51.58</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>47.69</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>47.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>141265.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>225541.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>225541.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>354816.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>754339.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>754339.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-185798.2351603996</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>141265</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>141265.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>46.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.19</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>47.52</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.19</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>47.52</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>163516.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>258309.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>258309.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>470557.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>752823.34</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>752823.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-183529.3073428617</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>163516</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>163516.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>46.67</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.51</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>47.36</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.51</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>47.36</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>127895.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>309053.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>309053</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>863925.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>750375.46</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>750375.46</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-176117.3994841338</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>127895</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>127895.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>48.11</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>47.22</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>47.22</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>230457.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>377395.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>377395.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1038086.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>748807.88</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>748807.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-155422.5168472321</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>230457</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>230457.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.68</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>47.12</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>464574.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>395693.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>395693.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1129464.1</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>745315.54</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>745315.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-131296.3803356857</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>464574</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>464574.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>51.76000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>46.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>46.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>305106.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>484092.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>484092</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1175832.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>737857.46</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>737857.46</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-117225.2788786306</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>305106</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>305106.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>53.74000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>52.61</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>46.77</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>52.61</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>46.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>417233.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>682806.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>682806</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1192750.8</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>732695.38</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>732695.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-75851.23112288641</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>417233</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>417233.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>55.38</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.54</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>469607.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1418798.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>1418798.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1210220.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>725481.54</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>725481.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-26050.08321743459</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>469607</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>469607.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>56.62</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>52.25</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.24</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.24</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>321946.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1698777.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1698777.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1236211.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>719386.26</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>719386.26</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>40413.27390526235</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>321946</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>321946.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>56.58000000000001</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>51.89</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>906568.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1863235.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1863235</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1401013.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>715148.3</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>715148.3</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>149738.4171553557</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>906568</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>906568.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>56.44</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>51.26</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.65</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>51.26</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.65</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1298676.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1867572.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1867572.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1665281.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>698393.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>698393.9399999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>237931.3211856545</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1298676</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1298676.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>217717</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>149413</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>216732</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>221658</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>301588</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>199194</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>216632</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>357016</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>609988</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>600689</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>797538</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>321219</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>681031</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>49.72</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>50.33</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>53.92</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>53.92</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>107700126.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>86357381.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>86357381.59999999</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>100320678.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>182133103.66</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>182133103.66</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-8263406.04873997</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>107700126</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>107700126.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>49.1</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>50.43</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>54.04</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>54.04</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>60823449.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>81241622.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>81241622.59999999</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>117388809.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>189015386.14</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>189015386.14</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-10622828.5067571</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>60823449</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>60823449.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>48.98999999999999</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>50.66</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>54.25</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>54.25</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>69838283.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>93039250.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>93039250</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>124235834.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>191023584.66</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>191023584.66</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-8591544.178683102</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>69838283</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>69838283.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>49.45</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>50.95</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>54.5</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>54.5</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>95116710.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>96589348.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>96589348.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>123752540.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>194833148.14</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>194833148.14</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-6348743.632195875</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>95116710</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>95116710.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>54.76</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>54.76</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>98308340.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>109594965.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>109594965</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>122107918.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>196916908.32</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>196916908.32</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-5626404.900349945</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>98308340</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>98308340.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>50.14</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>51.46</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>55.01</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>82121331.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>114283976.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>114283976.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>118415065.5</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>197976459.8</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>197976459.8</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-4735509.751271844</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>82121331</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>82121331.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>50.76000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>51.79</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>55.26</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>55.26</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>119811586.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>153535996.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>153535996.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>120980569.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>201107188.6</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>201107188.6</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1559354.654329136</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>119811586</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>119811586.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>51.08</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>52.07</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>55.53</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>52.07</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>55.53</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>87588774.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>155432419.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>155432419.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>125405933.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>205558005.9</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>205558005.9</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1004540.599613518</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>87588774</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>87588774.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>50.75</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>52.23</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>55.72</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>55.72</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>160144794.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>150915732.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>150915732.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>127224014.2</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>209589769.68</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>209589769.68</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>3276371.499966443</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>160144794</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>160144794.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>50.51000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>52.48</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>55.95</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>55.95</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>121753396.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>134620872.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>134620872</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>118542095.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>216718991.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>216718991.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>1501087.660081834</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>121753396</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>121753396.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>50.15</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>52.57</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>56.17</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>56.17</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>278381432.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>122546154.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>122546154.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>120270489.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>219412638.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>219412638.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>3024721.68667236</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>278381432</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>278381432.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/中央處理器.xlsx
+++ b/Result/checksun_type/中央處理器.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5731.0</t>
+          <t>16187.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -1163,47 +1163,47 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-1.62</v>
+        <v>3.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>51.38</v>
+        <v>51.36</v>
       </c>
       <c r="BA2" t="n">
-        <v>50.97</v>
+        <v>51.09</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-94.21</t>
+          <t>-93.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>295661.0</t>
+          <t>865699.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>337995.8</v>
+        <v>471553</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>292733.3</t>
+          <t>360776.4</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>646677.74</v>
+        <v>652783.34</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-26658.27339488786</t>
+          <t>-16481.05238828245</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-1257.527134713717</t>
+          <t>39493.66314804729</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>295661.0</t>
+          <t>865699.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7037.0</t>
+          <t>5731.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1641,56 +1641,56 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>58.62</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.42</v>
+        <v>-1.62</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>51.39</v>
+        <v>51.38</v>
       </c>
       <c r="BA3" t="n">
-        <v>50.85</v>
+        <v>50.97</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-94.31</t>
+          <t>-94.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>371873.0</t>
+          <t>295661.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>329058</v>
+        <v>337995.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>276455.4</t>
+          <t>292733.3</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>645018.24</v>
+        <v>646677.74</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>52602</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-31276.5908967377</t>
+          <t>-26658.27339488786</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>1646.898430438945</t>
+          <t>-1257.527134713717</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>371873.0</t>
+          <t>295661.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10605.0</t>
+          <t>7037.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,33 +2092,33 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2128,56 +2128,56 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>58.62</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.77</v>
+        <v>-0.42</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>51.92</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>51.13</v>
+        <v>51.39</v>
       </c>
       <c r="BA4" t="n">
-        <v>50.73</v>
+        <v>50.85</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-94.66</t>
+          <t>-94.31</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>565267.0</t>
+          <t>371873.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>357362.4</v>
+        <v>329058</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>276731.8</t>
+          <t>276455.4</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>643761.52</v>
+        <v>645018.24</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-37262.67986531527</t>
+          <t>-31276.5908967377</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2428.31142043008</t>
+          <t>1646.898430438945</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>565267.0</t>
+          <t>371873.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,34 +2252,34 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="CA4" t="inlineStr">
         <is>
           <t>8.289176239827855</t>
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4973.0</t>
+          <t>10605.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,33 +2579,33 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2615,56 +2615,56 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.78</v>
+        <v>1.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.09</v>
+        <v>1.66</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>51.98</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>50.85</v>
+        <v>51.13</v>
       </c>
       <c r="BA5" t="n">
-        <v>50.62</v>
+        <v>50.73</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-95.13</t>
+          <t>-94.66</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>259265.0</t>
+          <t>565267.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>274402.6</v>
+        <v>357362.4</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>243926.3</t>
+          <t>276731.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>644458.24</v>
+        <v>643761.52</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-43596.20140074895</t>
+          <t>-37262.67986531527</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-28884.10008522763</t>
+          <t>-2428.31142043008</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>259265.0</t>
+          <t>565267.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3808.0</t>
+          <t>4973.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,33 +3066,33 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3102,56 +3102,56 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1.91</v>
+        <v>-0.78</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>51.22000000000001</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50.61</v>
+        <v>50.85</v>
       </c>
       <c r="BA6" t="n">
-        <v>50.55</v>
+        <v>50.62</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.71</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-95.13</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>197913.0</t>
+          <t>259265.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>249999.8</v>
+        <v>274402.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>233146.7</t>
+          <t>243926.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>647074.86</v>
+        <v>644458.24</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-46271.12891266192</t>
+          <t>-43596.20140074895</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-32860.58031760884</t>
+          <t>-28884.10008522763</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>197913.0</t>
+          <t>259265.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4805.0</t>
+          <t>3808.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3553,33 +3553,33 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3589,56 +3589,56 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>76.37</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.22000000000001</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>50.3</v>
+        <v>50.61</v>
       </c>
       <c r="BA7" t="n">
-        <v>50.45</v>
+        <v>50.55</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>250972.0</t>
+          <t>197913.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>247470.8</v>
+        <v>249999.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>224830.1</t>
+          <t>233146.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>660034.46</v>
+        <v>647074.86</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-48709.41047539884</t>
+          <t>-46271.12891266192</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-30794.24563823885</t>
+          <t>-32860.58031760884</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>250972.0</t>
+          <t>197913.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9869.0</t>
+          <t>4805.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,74 +3885,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10.07</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-12-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>53.7</t>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,7 +4066,7 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4076,56 +4076,56 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>76.37</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>2.77</v>
+        <v>1.57</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>50.05</v>
+        <v>50.3</v>
       </c>
       <c r="BA8" t="n">
-        <v>50.34</v>
+        <v>50.45</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-96.09</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>513395.0</t>
+          <t>250972.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>223852.8</v>
+        <v>247470.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>222755.2</t>
+          <t>224830.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>665023.58</v>
+        <v>660034.46</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-51966.71317306429</t>
+          <t>-48709.41047539884</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-32427.43732348742</t>
+          <t>-30794.24563823885</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>513395.0</t>
+          <t>250972.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4340,14 +4340,14 @@
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>9869.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,22 +4382,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,7 +4553,7 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4563,56 +4563,56 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>47.04</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.24</v>
+        <v>2.77</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.67</v>
+        <v>1.1</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>50.12</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>49.79</v>
+        <v>50.05</v>
       </c>
       <c r="BA9" t="n">
-        <v>50.17</v>
+        <v>50.34</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.07</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-96.25</t>
+          <t>-96.09</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>150468.0</t>
+          <t>513395.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>196101.2</v>
+        <v>223852.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>196367.0</t>
+          <t>222755.2</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>657305.14</v>
+        <v>665023.58</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-265</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-55519.30878207827</t>
+          <t>-51966.71317306429</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-61719.19554086088</t>
+          <t>-32427.43732348742</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>150468.0</t>
+          <t>513395.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2701.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,149 +4859,149 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-0.14</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-12-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3.79</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/10/03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>45.95</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/04/15</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/12/23</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>50.1</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-6.70</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/10/03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/04/15</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>60.3</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/12/23</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
       <c r="AI10" t="inlineStr">
         <is>
           <t>2025/11/17</t>
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-09 00:00:00</t>
+          <t>2025-11-11 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,7 +5040,7 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5050,57 +5050,57 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>47.04</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.67</v>
+        <v>-0.24</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.77</v>
+        <v>0.67</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.44</t>
+          <t>50.12</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.56</v>
+        <v>49.79</v>
       </c>
       <c r="BA10" t="n">
-        <v>50.04</v>
+        <v>50.17</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>47.07</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="BD10" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BE10" t="n">
         <v>0.33</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0.34</v>
-      </c>
       <c r="BF10" t="inlineStr">
         <is>
           <t>8.67</t>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-96.11</t>
+          <t>-96.25</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>681247.1673553719</t>
+          <t>1002125.901639344</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>137251.0</t>
+          <t>150468.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>213450</v>
+        <v>196101.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>207913.8</t>
+          <t>196367.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>661386.96</v>
+        <v>657305.14</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>-265</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-54392.05664411779</t>
+          <t>-55519.30878207827</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-62475.27172493504</t>
+          <t>-61719.19554086088</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>137251.0</t>
+          <t>150468.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5284,24 +5284,24 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
           <t>17.23</t>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2429.0</t>
+          <t>10905.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,74 +5346,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>65.04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>57.4</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>6.32</v>
+        <v>10.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
       <c r="BA11" t="n">
-        <v>52.79</v>
+        <v>52.98</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>110.61</t>
+          <t>313.22</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.63</v>
+        <v>-0.35</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-116.64</t>
+          <t>-109.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>205743</v>
+        <v>329375.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>139611.1</t>
+          <t>199569.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>222614.5</v>
+        <v>233511.96</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>66131</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-9020.19988810568</t>
+          <t>-394.1269517676747</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>12815.11317058292</t>
+          <t>47049.27419809136</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>46.70</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8118.0</t>
+          <t>2429.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,22 +5843,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>7.72</v>
+        <v>6.32</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.4</v>
+        <v>2.28</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52.01</v>
+        <v>52.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>52.66</v>
+        <v>52.79</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>110.61</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-116.64</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>189517.4</v>
+        <v>205743</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>133155.2</t>
+          <t>139611.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>221511.36</v>
+        <v>222614.5</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-12990.25680786724</t>
+          <t>-9020.19988810568</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>19842.4862323358</t>
+          <t>12815.11317058292</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>46.70</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5690.0</t>
+          <t>8118.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.94</v>
+        <v>-0.4</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>52.07</v>
+        <v>52.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>52.54</v>
+        <v>52.66</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-124.22</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>123618.4</v>
+        <v>189517.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>92094.8</t>
+          <t>133155.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>213489.6</v>
+        <v>221511.36</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-18959.84645154052</t>
+          <t>-12990.25680786724</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-4800.033902029216</t>
+          <t>19842.4862323358</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>5690.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>-4.74</v>
+        <v>-2.94</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>52.11</v>
+        <v>52.07</v>
       </c>
       <c r="BA14" t="n">
-        <v>52.44</v>
+        <v>52.54</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-1.23</v>
+        <v>-0.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-125.03</t>
+          <t>-124.22</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>80214.39999999999</v>
+        <v>123618.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>70704.0</t>
+          <t>92094.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>209175.5</v>
+        <v>213489.6</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-21534.35782417894</t>
+          <t>-18959.84645154052</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-23728.20431176394</t>
+          <t>-4800.033902029216</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,149 +7294,149 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18.87</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/03/14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>32.85</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>11.99</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-11.61</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/03/14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>2025/10/20</t>
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="AV15" t="n">
-        <v>-5.36</v>
+        <v>-4.74</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>52.38</v>
+        <v>52.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>52.46</v>
+        <v>52.44</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-29.04</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-123.21</t>
+          <t>-125.03</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>69764.2</v>
+        <v>80214.39999999999</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>78924.9</t>
+          <t>70704.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>210122.46</v>
+        <v>209175.5</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-9160</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-21135.47664461804</t>
+          <t>-21534.35782417894</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-27083.51188596481</t>
+          <t>-23728.20431176394</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1120.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.85</v>
+        <v>0.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>-5.92</v>
+        <v>-5.36</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>52.58</v>
+        <v>52.38</v>
       </c>
       <c r="BA16" t="n">
         <v>52.46</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.79</v>
+        <v>-0.88</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-123.21</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>73479.2</v>
+        <v>69764.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>119450.5</t>
+          <t>78924.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>212397.56</v>
+        <v>210122.46</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-45971</t>
+          <t>-9160</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-20054.0156916459</t>
+          <t>-21135.47664461804</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-26037.54013889589</t>
+          <t>-27083.51188596481</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2486.0</t>
+          <t>1120.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.18</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.02</v>
+        <v>-0.85</v>
       </c>
       <c r="AV17" t="n">
-        <v>-6.34</v>
+        <v>-5.92</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49.51000000000001</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>52.86</v>
+        <v>52.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>52.54</v>
+        <v>52.46</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-87.87</t>
+          <t>-64.29</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-117.42</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>76793</v>
+        <v>73479.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>124218.1</t>
+          <t>119450.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>213523.76</v>
+        <v>212397.56</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-47425</t>
+          <t>-45971</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-18966.10215578226</t>
+          <t>-20054.0156916459</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-24761.63263812255</t>
+          <t>-26037.54013889589</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,42 +8740,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2486.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1713.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>11.64</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-38.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.56</v>
+        <v>-0.02</v>
       </c>
       <c r="AV18" t="n">
-        <v>-7.14</v>
+        <v>-6.34</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.51000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.12</v>
+        <v>52.86</v>
       </c>
       <c r="BA18" t="n">
-        <v>52.62</v>
+        <v>52.54</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-133.25</t>
+          <t>-87.87</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.52</v>
+        <v>-0.66</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-117.42</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>60571.2</v>
+        <v>76793</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>138654.5</t>
+          <t>124218.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>215595.82</v>
+        <v>213523.76</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-78083</t>
+          <t>-47425</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-17912.3693408113</t>
+          <t>-18966.10215578226</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-29416.77789994201</t>
+          <t>-24761.63263812255</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-66.67</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.61</v>
+        <v>1.56</v>
       </c>
       <c r="AV19" t="n">
-        <v>-7.97</v>
+        <v>-7.14</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.33</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.24</v>
+        <v>53.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>52.78</v>
+        <v>52.62</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.94</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-248.04</t>
+          <t>-133.25</t>
         </is>
       </c>
       <c r="BD19" t="n">
         <v>-1.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.34</v>
+        <v>-0.52</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-109.07</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>37991.0</t>
+          <t>86372.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>61193.6</v>
+        <v>60571.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>183607.2</t>
+          <t>138654.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>217110.84</v>
+        <v>215595.82</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-122413</t>
+          <t>-78083</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-15820.65869369663</t>
+          <t>-17912.3693408113</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-30963.27906325758</t>
+          <t>-29416.77789994201</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>37991.0</t>
+          <t>86372.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9672,17 +9672,17 @@
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2264.67</t>
+          <t>2919.098</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-21.34</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-60.31</t>
+          <t>-59.92</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,75 +9910,75 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.32</v>
+        <v>0.23</v>
       </c>
       <c r="AV20" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>51.67999999999999</t>
+          <t>51.38</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>56.82</v>
+        <v>56.55</v>
       </c>
       <c r="BA20" t="n">
-        <v>53.31</v>
+        <v>53.24</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>54.64</t>
+          <t>54.52</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3561.63</t>
+          <t>-458.82</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.88</v>
+        <v>-0.97</v>
       </c>
       <c r="BE20" t="n">
-        <v>0.03</v>
+        <v>-0.17</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-99.83</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>115796428.0</t>
+          <t>150205525.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>148011192.8</v>
+        <v>151715749.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>188158118.7</t>
+          <t>181596746.5</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>279750415.96</v>
+        <v>280873788.78</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-40146925</t>
+          <t>-29880996</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-35955621.4530187</t>
+          <t>-40269528.38341566</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-68391601.39546657</t>
+          <t>-63996016.50059894</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>115796428.0</t>
+          <t>150205525.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>-19.66</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
           <t>51.5</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>51.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3487.15</t>
+          <t>2264.67</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-21.34</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-60.47</t>
+          <t>-60.31</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10371,22 +10371,22 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,75 +10397,75 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-2.5</v>
+        <v>-1.32</v>
       </c>
       <c r="AV21" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.67999999999999</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>56.86</v>
+        <v>56.82</v>
       </c>
       <c r="BA21" t="n">
-        <v>53.36</v>
+        <v>53.31</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>54.78</t>
+          <t>54.64</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-380.58</t>
+          <t>-3561.63</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.71</v>
+        <v>-0.88</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-98.29</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>177730522.0</t>
+          <t>115796428.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>159600690.2</v>
+        <v>148011192.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>192113816.6</t>
+          <t>188158118.7</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>280961613.78</v>
+        <v>279750415.96</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-32513126</t>
+          <t>-40146925</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-30058170.55439182</t>
+          <t>-35955621.4530187</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-68541762.23115364</t>
+          <t>-68391601.39546657</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>177730522.0</t>
+          <t>115796428.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-20.75</t>
+          <t>-20.44</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3071.005</t>
+          <t>3487.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-59.92</t>
+          <t>-60.47</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10858,22 +10858,22 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,12 +10884,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -10903,56 +10903,56 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2.09</v>
+        <v>-2.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>-7.59</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>56.92</v>
+        <v>56.86</v>
       </c>
       <c r="BA22" t="n">
-        <v>53.45</v>
+        <v>53.36</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>54.92</t>
+          <t>54.78</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-192.46</t>
+          <t>-380.58</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.45</v>
+        <v>-0.71</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-96.66</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>159286955.0</t>
+          <t>177730522.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>163141459.2</v>
+        <v>159600690.2</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>195113552.2</t>
+          <t>192113816.6</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>278932283.02</v>
+        <v>280961613.78</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-31972093</t>
+          <t>-32513126</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-23061153.88588967</t>
+          <t>-30058170.55439182</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-72944153.41673684</t>
+          <t>-68541762.23115364</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>159286955.0</t>
+          <t>177730522.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-19.66</t>
+          <t>-20.75</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2966.391</t>
+          <t>3071.005</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-59.46</t>
+          <t>-59.92</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11345,22 +11345,22 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,56 +11390,56 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-2.1</v>
+        <v>-2.09</v>
       </c>
       <c r="AV23" t="n">
-        <v>-6.5</v>
+        <v>-7.59</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>53.22000000000001</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
         <v>56.92</v>
       </c>
       <c r="BA23" t="n">
-        <v>53.52</v>
+        <v>53.45</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>55.04</t>
+          <t>54.92</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-127.08</t>
+          <t>-192.46</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-95.05</t>
+          <t>-88.49</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>155559319.0</t>
+          <t>159286955.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>174911358</v>
+        <v>163141459.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>215246662.0</t>
+          <t>195113552.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>278875194.48</v>
+        <v>278932283.02</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-40335304</t>
+          <t>-31972093</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-13991517.60755382</t>
+          <t>-23061153.88588967</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-74652038.88125795</t>
+          <t>-72944153.41673684</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>155559319.0</t>
+          <t>159286955.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-19.66</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2506.692</t>
+          <t>2966.391</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-58.75</t>
+          <t>-59.46</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11832,22 +11832,22 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,56 +11877,56 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-1.56</v>
+        <v>-2.1</v>
       </c>
       <c r="AV24" t="n">
-        <v>-5.29</v>
+        <v>-6.5</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>53.84000000000001</t>
+          <t>53.22000000000001</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>56.85</v>
+        <v>56.92</v>
       </c>
       <c r="BA24" t="n">
-        <v>53.57</v>
+        <v>53.52</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>55.04</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-127.08</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-93.47</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>131682740.0</t>
+          <t>155559319.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>211477743.2</v>
+        <v>174911358</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>247260867.7</t>
+          <t>215246662.0</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>277609950.64</v>
+        <v>278875194.48</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-35783124</t>
+          <t>-40335304</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-2962331.921425791</t>
+          <t>-13991517.60755382</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-74026341.44195747</t>
+          <t>-74652038.88125795</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>131682740.0</t>
+          <t>155559319.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-17.32</t>
+          <t>-18.72</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
           <t>52.1</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3238.922</t>
+          <t>2506.692</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-58.68</t>
+          <t>-58.75</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12319,22 +12319,22 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,56 +12364,56 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-3.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AV25" t="n">
-        <v>-3.46</v>
+        <v>-5.29</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>54.77999999999999</t>
+          <t>53.84000000000001</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>56.74</v>
+        <v>56.85</v>
       </c>
       <c r="BA25" t="n">
-        <v>53.6</v>
+        <v>53.57</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-72.47</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-91.97</t>
+          <t>-77.54</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>173743915.0</t>
+          <t>131682740.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>228305044.6</v>
+        <v>211477743.2</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>280140569.8</t>
+          <t>247260867.7</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>277468280.18</v>
+        <v>277609950.64</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-51835525</t>
+          <t>-35783124</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>9958397.082307242</t>
+          <t>-2962331.921425791</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-67930485.15574402</t>
+          <t>-74026341.44195747</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>173743915.0</t>
+          <t>131682740.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.32</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>53.0</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>53.1</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3635.227</t>
+          <t>3238.922</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-41.09</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-58.52</t>
+          <t>-58.68</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12806,22 +12806,22 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,56 +12851,56 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-3.83</v>
+        <v>-3.07</v>
       </c>
       <c r="AV26" t="n">
-        <v>-2.24</v>
+        <v>-3.46</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>55.41999999999999</t>
+          <t>54.77999999999999</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>56.69</v>
+        <v>56.74</v>
       </c>
       <c r="BA26" t="n">
-        <v>53.64</v>
+        <v>53.6</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-54.69</t>
+          <t>-72.47</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-90.51</t>
+          <t>-72.35</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>195434367.0</t>
+          <t>173743915.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>224626943</v>
+        <v>228305044.6</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>381300939.9</t>
+          <t>280140569.8</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>278484305.54</v>
+        <v>277468280.18</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-156673996</t>
+          <t>-51835525</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>24120012.0346802</t>
+          <t>9958397.082307242</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-61302584.74130535</t>
+          <t>-67930485.15574402</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>195434367.0</t>
+          <t>173743915.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-16.85</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3968.501</t>
+          <t>3635.227</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-58.41</t>
+          <t>-41.09</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-57.51</t>
+          <t>-58.52</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13293,22 +13293,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13334,60 +13334,60 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-2.36</v>
+        <v>-3.83</v>
       </c>
       <c r="AV27" t="n">
-        <v>-1.18</v>
+        <v>-2.24</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.41999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>56.59</v>
+        <v>56.69</v>
       </c>
       <c r="BA27" t="n">
-        <v>53.65</v>
+        <v>53.64</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-37.29</t>
+          <t>-54.69</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-89.21</t>
+          <t>-67.34</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>218136449.0</t>
+          <t>195434367.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>227085645.2</v>
+        <v>224626943</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>546002122.2</t>
+          <t>381300939.9</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>277075349.9</v>
+        <v>278484305.54</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-318916477</t>
+          <t>-156673996</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>39651393.26667757</t>
+          <t>24120012.0346802</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-51968754.55134636</t>
+          <t>-61302584.74130535</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>218136449.0</t>
+          <t>195434367.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-14.82</t>
+          <t>-16.85</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6030.962</t>
+          <t>3968.501</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-68.08</t>
+          <t>-58.41</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-57.04</t>
+          <t>-57.51</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2024-10-09 00:00:00</t>
+          <t>2025-12-11 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-5.43</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,60 +13821,60 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-2.13</v>
+        <v>-2.36</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.06</v>
+        <v>-1.18</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>56.44</v>
+        <v>56.59</v>
       </c>
       <c r="BA28" t="n">
-        <v>53.64</v>
+        <v>53.65</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.49</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-24.44</t>
+          <t>-37.29</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>-62.88</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>2015368469.545455</t>
+          <t>1154905002.451844</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>338391245.0</t>
+          <t>218136449.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>255581966</v>
+        <v>227085645.2</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>800581992.9</t>
+          <t>546002122.2</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>276731957.2</v>
+        <v>277075349.9</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-545000026</t>
+          <t>-318916477</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>56309601.96086375</t>
+          <t>39651393.26667757</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-39211050.40314257</t>
+          <t>-51968754.55134636</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>338391245.0</t>
+          <t>218136449.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-13.88</t>
+          <t>-14.82</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>155.01</t>
+          <t>160.69</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/中央處理器.xlsx
+++ b/Result/checksun_type/中央處理器.xlsx
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>-4.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16187.0</t>
+          <t>7460.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,17 +973,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>28.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1118,22 +1118,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>16.70</t>
+          <t>7.70</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,66 +1144,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>52.01</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>3.8</v>
+        <v>-1.07</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>52.12</t>
+          <t>52.26000000000001</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>51.36</v>
+        <v>51.26</v>
       </c>
       <c r="BA2" t="n">
-        <v>51.09</v>
+        <v>51.07</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>48.57</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>17.13</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-93.70</t>
+          <t>-93.42</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,48 +1222,48 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>865699.0</t>
+          <t>390317.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>471553</v>
+        <v>497763.4</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>360776.4</t>
+          <t>386083.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>652783.34</v>
+        <v>640007.9</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>110776</t>
+          <t>111680</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-16481.05238828245</t>
+          <t>-9118.043595119172</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>39493.66314804729</t>
+          <t>31378.50476727885</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>865699.0</t>
+          <t>390317.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>51.3</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>50.7</t>
-        </is>
-      </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5731.0</t>
+          <t>16187.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.64</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.46</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1605,22 +1605,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>16.70</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-3.73</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1650,47 +1650,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.62</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.71</v>
+        <v>1.49</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>52.12</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>51.38</v>
+        <v>51.36</v>
       </c>
       <c r="BA3" t="n">
-        <v>50.97</v>
+        <v>51.09</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>48.21</t>
+          <t>48.41</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.53</v>
+        <v>0.72</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-94.21</t>
+          <t>-93.70</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,48 +1709,48 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>295661.0</t>
+          <t>865699.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>337995.8</v>
+        <v>471553</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>292733.3</t>
+          <t>360776.4</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>646677.74</v>
+        <v>652783.34</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>45262</t>
+          <t>110776</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-26658.27339488786</t>
+          <t>-16481.05238828245</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-1257.527134713717</t>
+          <t>39493.66314804729</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>295661.0</t>
+          <t>865699.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7037.0</t>
+          <t>5731.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>15.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2092,22 +2092,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-3.73</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>58.62</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.42</v>
+        <v>-1.62</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>51.39</v>
+        <v>51.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>50.85</v>
+        <v>50.97</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>48.21</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>24.54</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-94.31</t>
+          <t>-94.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,48 +2196,48 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>371873.0</t>
+          <t>295661.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>329058</v>
+        <v>337995.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>276455.4</t>
+          <t>292733.3</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>645018.24</v>
+        <v>646677.74</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>52602</t>
+          <t>45262</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-31276.5908967377</t>
+          <t>-26658.27339488786</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>1646.898430438945</t>
+          <t>-1257.527134713717</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>371873.0</t>
+          <t>295661.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10605.0</t>
+          <t>7037.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2579,92 +2579,92 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-6.19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>58.62</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>84.62</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.77</v>
+        <v>-0.42</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>51.98</t>
+          <t>51.92</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>51.13</v>
+        <v>51.39</v>
       </c>
       <c r="BA5" t="n">
-        <v>50.73</v>
+        <v>50.85</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.06</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-94.66</t>
+          <t>-94.31</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,48 +2683,48 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>565267.0</t>
+          <t>371873.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>357362.4</v>
+        <v>329058</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>276731.8</t>
+          <t>276455.4</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>643761.52</v>
+        <v>645018.24</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-37262.67986531527</t>
+          <t>-31276.5908967377</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2428.31142043008</t>
+          <t>1646.898430438945</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>565267.0</t>
+          <t>371873.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2739,34 +2739,34 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>擎亞</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>電子通路業</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>擎亞</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>電子通路業</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
       <c r="CA5" t="inlineStr">
         <is>
           <t>8.289176239827855</t>
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4973.0</t>
+          <t>10605.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3066,92 +3066,92 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-5.10</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>82.32</t>
+          <t>84.62</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.78</v>
+        <v>1.77</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.09</v>
+        <v>1.66</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>51.98</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>50.85</v>
+        <v>51.13</v>
       </c>
       <c r="BA6" t="n">
-        <v>50.62</v>
+        <v>50.73</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-95.13</t>
+          <t>-94.66</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,48 +3170,48 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>259265.0</t>
+          <t>565267.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>274402.6</v>
+        <v>357362.4</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>243926.3</t>
+          <t>276731.8</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>644458.24</v>
+        <v>643761.52</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>80630</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-43596.20140074895</t>
+          <t>-37262.67986531527</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-28884.10008522763</t>
+          <t>-2428.31142043008</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>259265.0</t>
+          <t>565267.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-2.30</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,22 +3271,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3808.0</t>
+          <t>4973.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3553,92 +3553,92 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>-5.10</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>53.85</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>82.32</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.91</v>
+        <v>-0.78</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>51.22000000000001</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>50.61</v>
+        <v>50.85</v>
       </c>
       <c r="BA7" t="n">
-        <v>50.55</v>
+        <v>50.62</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>47.71</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>20.67</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-95.38</t>
+          <t>-95.13</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,48 +3657,48 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>197913.0</t>
+          <t>259265.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>249999.8</v>
+        <v>274402.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>233146.7</t>
+          <t>243926.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>647074.86</v>
+        <v>644458.24</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>30476</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-46271.12891266192</t>
+          <t>-43596.20140074895</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-32860.58031760884</t>
+          <t>-28884.10008522763</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>197913.0</t>
+          <t>259265.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.30</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,22 +3758,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4805.0</t>
+          <t>3808.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.07</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -4040,92 +4040,92 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>93.1</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>76.37</t>
+          <t>97.7</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.22000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>50.3</v>
+        <v>50.61</v>
       </c>
       <c r="BA8" t="n">
-        <v>50.45</v>
+        <v>50.55</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>47.55</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>27.69</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-95.80</t>
+          <t>-95.38</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,48 +4144,48 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>250972.0</t>
+          <t>197913.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>247470.8</v>
+        <v>249999.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>224830.1</t>
+          <t>233146.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>660034.46</v>
+        <v>647074.86</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>16853</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-48709.41047539884</t>
+          <t>-46271.12891266192</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-30794.24563823885</t>
+          <t>-32860.58031760884</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>250972.0</t>
+          <t>197913.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9869.0</t>
+          <t>4805.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,74 +4372,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>51.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.19</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10.07</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-12-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-12-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-12-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.16</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.44</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-12-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-12-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-12-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>52.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>53.7</t>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4527,22 +4527,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>10.18</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.1</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>76.37</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>2.77</v>
+        <v>1.57</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>50.05</v>
+        <v>50.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>50.34</v>
+        <v>50.45</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>27.69</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-96.09</t>
+          <t>-95.80</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,48 +4631,48 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>513395.0</t>
+          <t>250972.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>223852.8</v>
+        <v>247470.8</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>222755.2</t>
+          <t>224830.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>665023.58</v>
+        <v>660034.46</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>22640</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-51966.71317306429</t>
+          <t>-48709.41047539884</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-32427.43732348742</t>
+          <t>-30794.24563823885</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>513395.0</t>
+          <t>250972.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
           <t>51.0</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
-      </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4834,7 +4834,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>9869.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,27 +4869,27 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-11-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>10.18</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>47.04</t>
+          <t>58.15</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.24</v>
+        <v>2.77</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.67</v>
+        <v>1.1</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>50.12</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>49.79</v>
+        <v>50.05</v>
       </c>
       <c r="BA10" t="n">
-        <v>50.17</v>
+        <v>50.34</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>47.07</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>16.18</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-96.25</t>
+          <t>-96.09</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,48 +5118,48 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>1002125.901639344</t>
+          <t>1001273.855828221</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>150468.0</t>
+          <t>513395.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>196101.2</v>
+        <v>223852.8</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>196367.0</t>
+          <t>222755.2</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>657305.14</v>
+        <v>665023.58</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-265</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-55519.30878207827</t>
+          <t>-51966.71317306429</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-61719.19554086088</t>
+          <t>-32427.43732348742</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>150468.0</t>
+          <t>513395.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>55.93</t>
+          <t>56.81</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>33.56</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10905.0</t>
+          <t>5322.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>10.09</v>
+        <v>9.34</v>
       </c>
       <c r="AV11" t="n">
-        <v>6</v>
+        <v>10.78</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.45</v>
+        <v>52.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>52.98</v>
+        <v>53.27</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>50.75</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>313.22</t>
+          <t>8807.60</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.76</v>
+        <v>1.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.35</v>
+        <v>0.02</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.33</t>
+          <t>-99.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>662931.0</t>
+          <t>327958.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>329375.2</v>
+        <v>376918.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>199569.7</t>
+          <t>228566.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>233511.96</v>
+        <v>237746.18</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>148352</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-394.1269517676747</t>
+          <t>6545.581819641966</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>47049.27419809136</t>
+          <t>44713.98006239498</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>662931.0</t>
+          <t>327958.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>65.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2429.0</t>
+          <t>10905.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,74 +5833,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>65.04</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7.35</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>57.4</t>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6033,47 +6033,47 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>6.32</v>
+        <v>10.09</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
       <c r="BA12" t="n">
-        <v>52.79</v>
+        <v>52.98</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>110.61</t>
+          <t>313.22</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.63</v>
+        <v>-0.35</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-116.64</t>
+          <t>-109.33</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>205743</v>
+        <v>329375.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>139611.1</t>
+          <t>199569.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>222614.5</v>
+        <v>233511.96</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>66131</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-9020.19988810568</t>
+          <t>-394.1269517676747</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>12815.11317058292</t>
+          <t>47049.27419809136</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>46.70</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8118.0</t>
+          <t>2429.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>7.72</v>
+        <v>6.32</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.4</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>52.01</v>
+        <v>52.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>52.66</v>
+        <v>52.79</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>110.61</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-116.64</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,48 +6579,48 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>189517.4</v>
+        <v>205743</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>133155.2</t>
+          <t>139611.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>221511.36</v>
+        <v>222614.5</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-12990.25680786724</t>
+          <t>-9020.19988810568</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>19842.4862323358</t>
+          <t>12815.11317058292</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>46.70</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5690.0</t>
+          <t>8118.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.94</v>
+        <v>-0.4</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>52.07</v>
+        <v>52.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>52.54</v>
+        <v>52.66</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-124.22</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>123618.4</v>
+        <v>189517.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>92094.8</t>
+          <t>133155.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>213489.6</v>
+        <v>221511.36</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-18959.84645154052</t>
+          <t>-12990.25680786724</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4800.033902029216</t>
+          <t>19842.4862323358</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>5690.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>-4.74</v>
+        <v>-2.94</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>52.11</v>
+        <v>52.07</v>
       </c>
       <c r="BA15" t="n">
-        <v>52.44</v>
+        <v>52.54</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.23</v>
+        <v>-0.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-125.03</t>
+          <t>-124.22</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>80214.39999999999</v>
+        <v>123618.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>70704.0</t>
+          <t>92094.8</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>209175.5</v>
+        <v>213489.6</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-21534.35782417894</t>
+          <t>-18959.84645154052</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-23728.20431176394</t>
+          <t>-4800.033902029216</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,149 +7781,149 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025/03/14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>32.85</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-11.61</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025/03/14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>2025/10/20</t>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>-5.36</v>
+        <v>-4.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>52.38</v>
+        <v>52.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>52.46</v>
+        <v>52.44</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-29.04</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-123.21</t>
+          <t>-125.03</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>69764.2</v>
+        <v>80214.39999999999</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>78924.9</t>
+          <t>70704.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>210122.46</v>
+        <v>209175.5</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-9160</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-21135.47664461804</t>
+          <t>-21534.35782417894</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-27083.51188596481</t>
+          <t>-23728.20431176394</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1120.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.85</v>
+        <v>0.67</v>
       </c>
       <c r="AV17" t="n">
-        <v>-5.92</v>
+        <v>-5.36</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>52.58</v>
+        <v>52.38</v>
       </c>
       <c r="BA17" t="n">
         <v>52.46</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.79</v>
+        <v>-0.88</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-123.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>73479.2</v>
+        <v>69764.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>119450.5</t>
+          <t>78924.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>212397.56</v>
+        <v>210122.46</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-45971</t>
+          <t>-9160</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-20054.0156916459</t>
+          <t>-21135.47664461804</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-26037.54013889589</t>
+          <t>-27083.51188596481</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2486.0</t>
+          <t>1120.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.18</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.02</v>
+        <v>-0.85</v>
       </c>
       <c r="AV18" t="n">
-        <v>-6.34</v>
+        <v>-5.92</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49.51000000000001</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>52.86</v>
+        <v>52.58</v>
       </c>
       <c r="BA18" t="n">
-        <v>52.54</v>
+        <v>52.46</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-87.87</t>
+          <t>-64.29</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-117.42</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>76793</v>
+        <v>73479.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>124218.1</t>
+          <t>119450.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>213523.76</v>
+        <v>212397.56</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-47425</t>
+          <t>-45971</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-18966.10215578226</t>
+          <t>-20054.0156916459</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-24761.63263812255</t>
+          <t>-26037.54013889589</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>2486.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-38.18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.56</v>
+        <v>-0.02</v>
       </c>
       <c r="AV19" t="n">
-        <v>-7.14</v>
+        <v>-6.34</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.51000000000001</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.12</v>
+        <v>52.86</v>
       </c>
       <c r="BA19" t="n">
-        <v>52.62</v>
+        <v>52.54</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-133.25</t>
+          <t>-87.87</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.52</v>
+        <v>-0.66</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-117.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>60571.2</v>
+        <v>76793</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>138654.5</t>
+          <t>124218.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>215595.82</v>
+        <v>213523.76</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-78083</t>
+          <t>-47425</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-17912.3693408113</t>
+          <t>-18966.10215578226</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-29416.77789994201</t>
+          <t>-24761.63263812255</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2919.098</t>
+          <t>3195.907</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-16.45</t>
+          <t>-6.60</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-59.92</t>
+          <t>-60.62</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,17 +9910,17 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -9929,47 +9929,47 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>0.23</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>-9.140000000000001</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>51.38</t>
+          <t>51.08</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>56.55</v>
+        <v>55.96</v>
       </c>
       <c r="BA20" t="n">
-        <v>53.24</v>
+        <v>53.18</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-458.82</t>
+          <t>-206.38</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.97</v>
+        <v>-1.09</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-108.37</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>150205525.0</t>
+          <t>163284523.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>151715749.8</v>
+        <v>153260790.6</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>181596746.5</t>
+          <t>164086074.3</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>280873788.78</v>
+        <v>282326465.06</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-29880996</t>
+          <t>-10825283</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>-40269528.38341566</t>
+          <t>-43049336.60314812</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-63996016.50059894</t>
+          <t>-58338281.81167665</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>150205525.0</t>
+          <t>163284523.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-19.66</t>
+          <t>-21.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2264.67</t>
+          <t>2919.098</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.34</t>
+          <t>-16.45</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-60.31</t>
+          <t>-59.92</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.32</v>
+        <v>0.23</v>
       </c>
       <c r="AV21" t="n">
-        <v>-9.050000000000001</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>51.67999999999999</t>
+          <t>51.38</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>56.82</v>
+        <v>56.55</v>
       </c>
       <c r="BA21" t="n">
-        <v>53.31</v>
+        <v>53.24</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>54.64</t>
+          <t>54.52</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3561.63</t>
+          <t>-458.82</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.88</v>
+        <v>-0.97</v>
       </c>
       <c r="BE21" t="n">
-        <v>0.03</v>
+        <v>-0.17</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-99.40</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>115796428.0</t>
+          <t>150205525.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>148011192.8</v>
+        <v>151715749.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>188158118.7</t>
+          <t>181596746.5</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>279750415.96</v>
+        <v>280873788.78</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-40146925</t>
+          <t>-29880996</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>-35955621.4530187</t>
+          <t>-40269528.38341566</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-68391601.39546657</t>
+          <t>-63996016.50059894</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>115796428.0</t>
+          <t>150205525.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-20.44</t>
+          <t>-19.66</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>50.7</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
           <t>51.5</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>50.9</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>51.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3487.15</t>
+          <t>2264.67</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.92</t>
+          <t>-21.34</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-60.47</t>
+          <t>-60.31</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-2.5</v>
+        <v>-1.32</v>
       </c>
       <c r="AV22" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.67999999999999</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>56.86</v>
+        <v>56.82</v>
       </c>
       <c r="BA22" t="n">
-        <v>53.36</v>
+        <v>53.31</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>54.78</t>
+          <t>54.64</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-380.58</t>
+          <t>-3561.63</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.71</v>
+        <v>-0.88</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-94.10</t>
+          <t>-99.40</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>177730522.0</t>
+          <t>115796428.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>159600690.2</v>
+        <v>148011192.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>192113816.6</t>
+          <t>188158118.7</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>280961613.78</v>
+        <v>279750415.96</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-32513126</t>
+          <t>-40146925</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>-30058170.55439182</t>
+          <t>-35955621.4530187</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-68541762.23115364</t>
+          <t>-68391601.39546657</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>177730522.0</t>
+          <t>115796428.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-20.75</t>
+          <t>-20.44</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,42 +11175,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3487.15</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>-1.14</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>3071.005</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.39</t>
+          <t>-16.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-59.92</t>
+          <t>-60.47</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,12 +11371,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11390,47 +11390,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-2.09</v>
+        <v>-2.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>-7.59</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>56.92</v>
+        <v>56.86</v>
       </c>
       <c r="BA23" t="n">
-        <v>53.45</v>
+        <v>53.36</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>54.92</t>
+          <t>54.78</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-192.46</t>
+          <t>-380.58</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.45</v>
+        <v>-0.71</v>
       </c>
       <c r="BE23" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-88.49</t>
+          <t>-94.10</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>159286955.0</t>
+          <t>177730522.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>163141459.2</v>
+        <v>159600690.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>195113552.2</t>
+          <t>192113816.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>278932283.02</v>
+        <v>280961613.78</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-31972093</t>
+          <t>-32513126</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>-23061153.88588967</t>
+          <t>-30058170.55439182</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-72944153.41673684</t>
+          <t>-68541762.23115364</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>159286955.0</t>
+          <t>177730522.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-19.66</t>
+          <t>-20.75</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2966.391</t>
+          <t>3071.005</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.78</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-18.74</t>
+          <t>-16.39</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-59.46</t>
+          <t>-59.92</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,12 +11858,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11877,47 +11877,47 @@
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-2.1</v>
+        <v>-2.09</v>
       </c>
       <c r="AV24" t="n">
-        <v>-6.5</v>
+        <v>-7.59</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>53.22000000000001</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
         <v>56.92</v>
       </c>
       <c r="BA24" t="n">
-        <v>53.52</v>
+        <v>53.45</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>55.04</t>
+          <t>54.92</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-127.08</t>
+          <t>-192.46</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="BE24" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-88.49</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>155559319.0</t>
+          <t>159286955.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>174911358</v>
+        <v>163141459.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>215246662.0</t>
+          <t>195113552.2</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>278875194.48</v>
+        <v>278932283.02</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-40335304</t>
+          <t>-31972093</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>-13991517.60755382</t>
+          <t>-23061153.88588967</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-74652038.88125795</t>
+          <t>-72944153.41673684</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>155559319.0</t>
+          <t>159286955.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-18.72</t>
+          <t>-19.66</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2506.692</t>
+          <t>2966.391</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-18.74</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-58.75</t>
+          <t>-59.46</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,47 +12364,47 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-1.56</v>
+        <v>-2.1</v>
       </c>
       <c r="AV25" t="n">
-        <v>-5.29</v>
+        <v>-6.5</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>53.84000000000001</t>
+          <t>53.22000000000001</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>56.85</v>
+        <v>56.92</v>
       </c>
       <c r="BA25" t="n">
-        <v>53.57</v>
+        <v>53.52</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>55.04</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-92.39</t>
+          <t>-127.08</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>0.96</v>
+        <v>0.73</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-77.54</t>
+          <t>-82.95</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>131682740.0</t>
+          <t>155559319.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>211477743.2</v>
+        <v>174911358</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>247260867.7</t>
+          <t>215246662.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>277609950.64</v>
+        <v>278875194.48</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-35783124</t>
+          <t>-40335304</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>-2962331.921425791</t>
+          <t>-13991517.60755382</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-74026341.44195747</t>
+          <t>-74652038.88125795</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>131682740.0</t>
+          <t>155559319.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-17.32</t>
+          <t>-18.72</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>52.1</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>53.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3238.922</t>
+          <t>2506.692</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-58.68</t>
+          <t>-58.75</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-3.07</v>
+        <v>-1.56</v>
       </c>
       <c r="AV26" t="n">
-        <v>-3.46</v>
+        <v>-5.29</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>54.77999999999999</t>
+          <t>53.84000000000001</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>56.74</v>
+        <v>56.85</v>
       </c>
       <c r="BA26" t="n">
-        <v>53.6</v>
+        <v>53.57</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-72.47</t>
+          <t>-92.39</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-72.35</t>
+          <t>-77.54</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>173743915.0</t>
+          <t>131682740.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>228305044.6</v>
+        <v>211477743.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>280140569.8</t>
+          <t>247260867.7</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>277468280.18</v>
+        <v>277609950.64</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-51835525</t>
+          <t>-35783124</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>9958397.082307242</t>
+          <t>-2962331.921425791</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>-67930485.15574402</t>
+          <t>-74026341.44195747</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>173743915.0</t>
+          <t>131682740.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-17.16</t>
+          <t>-17.32</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CT26" t="inlineStr">
+        <is>
           <t>53.0</t>
-        </is>
-      </c>
-      <c r="CT26" t="inlineStr">
-        <is>
-          <t>53.1</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3635.227</t>
+          <t>3238.922</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-41.09</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-58.52</t>
+          <t>-58.68</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,12 +13319,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-3.83</v>
+        <v>-3.07</v>
       </c>
       <c r="AV27" t="n">
-        <v>-2.24</v>
+        <v>-3.46</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>5.68</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>55.41999999999999</t>
+          <t>54.77999999999999</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>56.69</v>
+        <v>56.74</v>
       </c>
       <c r="BA27" t="n">
-        <v>53.64</v>
+        <v>53.6</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>55.37</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-54.69</t>
+          <t>-72.47</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-67.34</t>
+          <t>-72.35</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>195434367.0</t>
+          <t>173743915.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>224626943</v>
+        <v>228305044.6</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>381300939.9</t>
+          <t>280140569.8</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>278484305.54</v>
+        <v>277468280.18</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>-156673996</t>
+          <t>-51835525</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>24120012.0346802</t>
+          <t>9958397.082307242</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>-61302584.74130535</t>
+          <t>-67930485.15574402</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>195434367.0</t>
+          <t>173743915.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-16.85</t>
+          <t>-17.16</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3968.501</t>
+          <t>3635.227</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-58.41</t>
+          <t>-41.09</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-57.51</t>
+          <t>-58.52</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13821,51 +13821,51 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-2.36</v>
+        <v>-3.83</v>
       </c>
       <c r="AV28" t="n">
-        <v>-1.18</v>
+        <v>-2.24</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.41999999999999</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>56.59</v>
+        <v>56.69</v>
       </c>
       <c r="BA28" t="n">
-        <v>53.65</v>
+        <v>53.64</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>55.37</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-37.29</t>
+          <t>-54.69</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-62.88</t>
+          <t>-67.34</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1154905002.451844</t>
+          <t>1153044106.300613</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>218136449.0</t>
+          <t>195434367.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>227085645.2</v>
+        <v>224626943</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>546002122.2</t>
+          <t>381300939.9</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>277075349.9</v>
+        <v>278484305.54</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>-318916477</t>
+          <t>-156673996</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>39651393.26667757</t>
+          <t>24120012.0346802</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>-51968754.55134636</t>
+          <t>-61302584.74130535</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>218136449.0</t>
+          <t>195434367.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-14.82</t>
+          <t>-16.85</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>160.69</t>
+          <t>159.34</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">
